--- a/Excel/Ejercicios/02- Datos.xlsx
+++ b/Excel/Ejercicios/02- Datos.xlsx
@@ -5,21 +5,32 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\NURIA\EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\NURIA\EXCEL\Ejercicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5078150A-9DF4-4D90-ADBF-9A4270DDFB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5F4E38-5C32-4EDF-BCAD-8F4676D81A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-113" yWindow="-113" windowWidth="20260" windowHeight="10769" activeTab="1" xr2:uid="{3F6E50A2-1EF4-4293-9D83-804CCBA67A06}"/>
+    <workbookView xWindow="-113" yWindow="-113" windowWidth="18257" windowHeight="10769" xr2:uid="{3F6E50A2-1EF4-4293-9D83-804CCBA67A06}"/>
   </bookViews>
   <sheets>
-    <sheet name="Formatos" sheetId="1" r:id="rId1"/>
-    <sheet name="Series" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -155,9 +166,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ACB902C-B412-486D-983C-4EB77C4EB315}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A2:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
@@ -488,143 +498,62 @@
     <col min="13" max="13" width="11.21875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -635,42 +564,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DBF4040-7936-434B-A8C8-B497019189FF}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A2:H23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" ht="51.65" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="1"/>
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
@@ -692,25 +603,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="3:8" ht="19.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="3:8" ht="19.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="3:8" ht="19.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="3:8" ht="19.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="3:8" ht="19.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="3:8" ht="19.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="3:8" ht="19.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="3:8" ht="19.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="3:8" ht="19.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="3:8" ht="19.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="3:8" ht="19.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="1:2" ht="19.45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:2" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="1:2" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -718,22 +616,20 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>22</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>27</v>
       </c>
